--- a/prototipo/matriz_documentos/data/matriz_documentos.xlsx
+++ b/prototipo/matriz_documentos/data/matriz_documentos.xlsx
@@ -8,13 +8,14 @@
   <sheets>
     <sheet name="metadados" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="matriz_longa" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="categorias" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="funcao_redistributiva" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="categorias" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="1041">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="1054">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -3092,6 +3093,45 @@
   </si>
   <si>
     <t xml:space="preserve">Transparência — qualquer cidadão pode consultar dados desagregados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tem_funcao_redistributiva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">como_redistribui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vincula recursos a educacao (art. 212 — 18% da Uniao e 25% de estados e municipios) e estabelece o regime de colaboracao com funcao redistributiva e supletiva da Uniao (art. 211, paragrafo 1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art. 9, X-XIII atribui a Uniao a responsabilidade de prestar assistencia tecnica e financeira a estados e municipios para garantir oferta com padrao minimo de qualidade.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica afirmativa nacional que equaliza acesso ao ensino superior publico federal — reserva 50% das vagas com subcotas por renda, raca/cor, PCD e (apos 2023) quilombolas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LBI determina ao poder publico assegurar oferta de educacao inclusiva com AEE, profissional de apoio e acessibilidade (art. 28) — vincula a Uniao a apoio tecnico e ao financiamento da rede.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diretriz III explicita superacao das desigualdades; metas 7 (qualidade), 8 (escolaridade media por raca/renda/territorio) e 20 (financiamento como % do PIB) operam logica redistributiva entre redes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instrumento redistributivo central — tres complementacoes da Uniao (VAAF, VAAT, VAAR) elevam o gasto-aluno em redes com menor capacidade fiscal. VAAR condiciona transferencia a melhoria de aprendizagem e a reducao de desigualdades (raca, NSE, PCD).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencia condicional da Uniao diretamente ao estudante (CadUnico/Bolsa Familia) com gatilhos de matricula, frequencia e conclusao — equaliza condicoes de permanencia no ensino medio publico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apoio financeiro e tecnico da Uniao para ampliar a matricula em tempo integral, com criterios redistributivos por vulnerabilidade territorial e socioeconomica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apoio tecnico e financeiro da Uniao para escolas do campo, assentados, quilombolas e ribeirinhos, com diretrizes proprias de infraestrutura, projeto pedagogico e formacao docente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criterios de apoio da Uniao consideram proporcao de criancas nao alfabetizadas, NSE, recortes etnico-raciais, genero e PCD — alocacao redistributiva por necessidade da rede.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aporta R$ 1,5 bi ate 2027 para implementar a Lei 10.639/2003 com criterios tecnicos por rede; inclui o Diagnostico Equidade em 100% das redes como condicao de monitoramento.</t>
   </si>
   <si>
     <t xml:space="preserve">chave_categoria</t>
@@ -11905,16 +11945,609 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
+    <col min="1" max="1" width="6.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="40.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="90.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>125</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>133</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>139</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>151</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>155</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>157</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>161</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>167</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>173</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>179</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>185</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>190</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>197</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>202</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>206</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>211</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>217</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>223</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>228</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>235</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>240</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>246</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>252</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>255</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
     <col min="1" max="1" width="28.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="32.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1026</v>
+        <v>1039</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1027</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="2">
@@ -11922,7 +12555,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>1028</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="3">
@@ -11930,7 +12563,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>1029</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="4">
@@ -11938,7 +12571,7 @@
         <v>87</v>
       </c>
       <c r="B4" t="s">
-        <v>1030</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="5">
@@ -11946,7 +12579,7 @@
         <v>99</v>
       </c>
       <c r="B5" t="s">
-        <v>1031</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="6">
@@ -11954,7 +12587,7 @@
         <v>126</v>
       </c>
       <c r="B6" t="s">
-        <v>1032</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="7">
@@ -11962,7 +12595,7 @@
         <v>105</v>
       </c>
       <c r="B7" t="s">
-        <v>1033</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="8">
@@ -11970,7 +12603,7 @@
         <v>134</v>
       </c>
       <c r="B8" t="s">
-        <v>1034</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="9">
@@ -11978,7 +12611,7 @@
         <v>146</v>
       </c>
       <c r="B9" t="s">
-        <v>1035</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="10">
@@ -11986,7 +12619,7 @@
         <v>162</v>
       </c>
       <c r="B10" t="s">
-        <v>1036</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="11">
@@ -11994,7 +12627,7 @@
         <v>191</v>
       </c>
       <c r="B11" t="s">
-        <v>1037</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="12">
@@ -12002,7 +12635,7 @@
         <v>212</v>
       </c>
       <c r="B12" t="s">
-        <v>1038</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="13">
@@ -12010,7 +12643,7 @@
         <v>229</v>
       </c>
       <c r="B13" t="s">
-        <v>1039</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="14">
@@ -12018,7 +12651,7 @@
         <v>247</v>
       </c>
       <c r="B14" t="s">
-        <v>1040</v>
+        <v>1053</v>
       </c>
     </row>
   </sheetData>

--- a/prototipo/matriz_documentos/data/matriz_documentos.xlsx
+++ b/prototipo/matriz_documentos/data/matriz_documentos.xlsx
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">Diretriz III explicita superacao das desigualdades; metas 7 (qualidade), 8 (escolaridade media por raca/renda/territorio) e 20 (financiamento como % do PIB) operam logica redistributiva entre redes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrumento redistributivo central — tres complementacoes da Uniao (VAAF, VAAT, VAAR) elevam o gasto-aluno em redes com menor capacidade fiscal. VAAR condiciona transferencia a melhoria de aprendizagem e a reducao de desigualdades (raca, NSE, PCD).</t>
+    <t xml:space="preserve">Instrumento redistributivo central do financiamento da educacao basica. A complementacao da Uniao e repartida em tres caminhos com logicas distintas: o VAAF eleva o valor por aluno em redes cujo fundo estadual ficou abaixo do minimo nacional (equalizacao vertical entre federados); o VAAT considera o total das receitas vinculadas a educacao e completa as redes em que o valor total ainda e insuficiente; o VAAR (art. 14, paragrafo 3o) e repartido entre as redes que cumprem condicionalidades de gestao (CACS-Fundeb ativo, plano de carreira docente atualizado, Lei do Piso cumprida, sistema de avaliacao institucional permanente, plano municipal ou estadual alinhado ao PNE) e demonstram melhoria na proficiencia do Saeb com reducao de desigualdade pelo Indicador de Equidade da Aprendizagem. A propria lei estabelece, assim, os instrumentos formais de medida da funcao redistributiva.</t>
   </si>
   <si>
     <t xml:space="preserve">Transferencia condicional da Uniao diretamente ao estudante (CadUnico/Bolsa Familia) com gatilhos de matricula, frequencia e conclusao — equaliza condicoes de permanencia no ensino medio publico.</t>
